--- a/Immigration_Networks/MigrationData/Matrices/MigrationMatrix_2000.xlsx
+++ b/Immigration_Networks/MigrationData/Matrices/MigrationMatrix_2000.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1402c53be3bc7c0d/Career/Professional_Portfolio/Network_Analysis/MigrationAmericas_NetworkAnalysis/Immigration_Networks/MigrationData/Matrices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E82EA62B-2AE6-4452-9738-EA1BBE15038D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{E82EA62B-2AE6-4452-9738-EA1BBE15038D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC26BDDE-50D6-4505-A351-C013972A9A6B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="13176" xr2:uid="{54F4A6BC-E46E-408A-A193-B52CFF00BC25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -99,10 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###\ ###\ ##0;\-###\ ###\ ##0;..;"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,19 +125,8 @@
       <family val="1"/>
       <scheme val="major"/>
     </font>
-    <font>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,24 +149,6 @@
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFBFBF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -220,10 +191,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -239,6 +207,1597 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="G1">
+            <v>2000</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>Matching</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="L2" t="str">
+            <v>Argentina_Bolivia</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="L3" t="str">
+            <v>Argentina_Brazil</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="L4" t="str">
+            <v>Argentina_Canada</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5" t="str">
+            <v>Argentina_Chile</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6" t="str">
+            <v>Argentina_Colombia</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="L7" t="str">
+            <v>Argentina_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="L8" t="str">
+            <v>Argentina_Ecuador</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="L9" t="str">
+            <v>Argentina_El Salvador</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="L10" t="str">
+            <v>Argentina_Guatemala</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="L11" t="str">
+            <v>Argentina_Honduras</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="L12" t="str">
+            <v>Argentina_Mexico</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="L13" t="str">
+            <v>Argentina_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="L14" t="str">
+            <v>Argentina_Panama</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="L15" t="str">
+            <v>Argentina_Paraguay</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="L16" t="str">
+            <v>Argentina_Peru</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="L17" t="str">
+            <v>Argentina_United States</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="L18" t="str">
+            <v>Argentina_Uruguay</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="L19" t="str">
+            <v>Argentina_Venezuela</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="L20" t="str">
+            <v>Bolivia_Argentina</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="L21" t="str">
+            <v>Bolivia_Brazil</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="L22" t="str">
+            <v>Bolivia_Canada</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="L23" t="str">
+            <v>Bolivia_Chile</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="L24" t="str">
+            <v>Bolivia_Colombia</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="L25" t="str">
+            <v>Bolivia_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="L26" t="str">
+            <v>Bolivia_Ecuador</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="L27" t="str">
+            <v>Bolivia_El Salvador</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="L28" t="str">
+            <v>Bolivia_Guatemala</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="L29" t="str">
+            <v>Bolivia_Honduras</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="L30" t="str">
+            <v>Bolivia_Mexico</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="L31" t="str">
+            <v>Bolivia_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="L32" t="str">
+            <v>Bolivia_Panama</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="L33" t="str">
+            <v>Bolivia_Paraguay</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="L34" t="str">
+            <v>Bolivia_Peru</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="L35" t="str">
+            <v>Bolivia_United States</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="L36" t="str">
+            <v>Bolivia_Uruguay</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="L37" t="str">
+            <v>Bolivia_Venezuela</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="L38" t="str">
+            <v>Brazil_Argentina</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="L39" t="str">
+            <v>Brazil_Bolivia</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="L40" t="str">
+            <v>Brazil_Canada</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="L41" t="str">
+            <v>Brazil_Chile</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="L42" t="str">
+            <v>Brazil_Colombia</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="L43" t="str">
+            <v>Brazil_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="L44" t="str">
+            <v>Brazil_Ecuador</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="L45" t="str">
+            <v>Brazil_El Salvador</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="L46" t="str">
+            <v>Brazil_Guatemala</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="L47" t="str">
+            <v>Brazil_Honduras</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="L48" t="str">
+            <v>Brazil_Mexico</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="L49" t="str">
+            <v>Brazil_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="L50" t="str">
+            <v>Brazil_Panama</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="L51" t="str">
+            <v>Brazil_Paraguay</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="L52" t="str">
+            <v>Brazil_Peru</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="L53" t="str">
+            <v>Brazil_United States</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="L54" t="str">
+            <v>Brazil_Uruguay</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="L55" t="str">
+            <v>Brazil_Venezuela</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="L56" t="str">
+            <v>Canada_Argentina</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="L57" t="str">
+            <v>Canada_Bolivia</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="L58" t="str">
+            <v>Canada_Brazil</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="L59" t="str">
+            <v>Canada_Chile</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="L60" t="str">
+            <v>Canada_Colombia</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="L61" t="str">
+            <v>Canada_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="L62" t="str">
+            <v>Canada_Ecuador</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="L63" t="str">
+            <v>Canada_El Salvador</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="L64" t="str">
+            <v>Canada_Guatemala</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="L65" t="str">
+            <v>Canada_Honduras</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="L66" t="str">
+            <v>Canada_Mexico</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="L67" t="str">
+            <v>Canada_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="L68" t="str">
+            <v>Canada_Panama</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="L69" t="str">
+            <v>Canada_Paraguay</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="L70" t="str">
+            <v>Canada_Peru</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="L71" t="str">
+            <v>Canada_United States</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="L72" t="str">
+            <v>Canada_Uruguay</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="L73" t="str">
+            <v>Canada_Venezuela</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="L74" t="str">
+            <v>Chile_Argentina</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="L75" t="str">
+            <v>Chile_Bolivia</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="L76" t="str">
+            <v>Chile_Brazil</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="L77" t="str">
+            <v>Chile_Colombia</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="L78" t="str">
+            <v>Chile_Ecuador</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="L79" t="str">
+            <v>Chile_Mexico</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="L80" t="str">
+            <v>Chile_Paraguay</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="L81" t="str">
+            <v>Chile_Peru</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="L82" t="str">
+            <v>Chile_United States</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="L83" t="str">
+            <v>Chile_Uruguay</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="L84" t="str">
+            <v>Chile_Venezuela</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="L85" t="str">
+            <v>Colombia_Argentina</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="L86" t="str">
+            <v>Colombia_Bolivia</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="L87" t="str">
+            <v>Colombia_Brazil</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="L88" t="str">
+            <v>Colombia_Canada</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="L89" t="str">
+            <v>Colombia_Chile</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="L90" t="str">
+            <v>Colombia_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="L91" t="str">
+            <v>Colombia_Ecuador</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="L92" t="str">
+            <v>Colombia_El Salvador</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="L93" t="str">
+            <v>Colombia_Guatemala</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="L94" t="str">
+            <v>Colombia_Honduras</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="L95" t="str">
+            <v>Colombia_Mexico</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="L96" t="str">
+            <v>Colombia_Panama</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="L97" t="str">
+            <v>Colombia_Peru</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="L98" t="str">
+            <v>Colombia_United States</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="L99" t="str">
+            <v>Colombia_Uruguay</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="L100" t="str">
+            <v>Colombia_Venezuela</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="L101" t="str">
+            <v>Costa Rica_Argentina</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="L102" t="str">
+            <v>Costa Rica_Bolivia</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="L103" t="str">
+            <v>Costa Rica_Brazil</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="L104" t="str">
+            <v>Costa Rica_Canada</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="L105" t="str">
+            <v>Costa Rica_Chile</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="L106" t="str">
+            <v>Costa Rica_Colombia</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="L107" t="str">
+            <v>Costa Rica_Ecuador</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="L108" t="str">
+            <v>Costa Rica_El Salvador</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="L109" t="str">
+            <v>Costa Rica_Guatemala</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="L110" t="str">
+            <v>Costa Rica_Honduras</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="L111" t="str">
+            <v>Costa Rica_Mexico</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="L112" t="str">
+            <v>Costa Rica_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="L113" t="str">
+            <v>Costa Rica_Panama</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="L114" t="str">
+            <v>Costa Rica_Paraguay</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="L115" t="str">
+            <v>Costa Rica_Peru</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="L116" t="str">
+            <v>Costa Rica_United States</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="L117" t="str">
+            <v>Costa Rica_Uruguay</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="L118" t="str">
+            <v>Costa Rica_Venezuela</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="L119" t="str">
+            <v>Ecuador_Argentina</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="L120" t="str">
+            <v>Ecuador_Bolivia</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="L121" t="str">
+            <v>Ecuador_Brazil</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="L122" t="str">
+            <v>Ecuador_Canada</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="L123" t="str">
+            <v>Ecuador_Chile</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="L124" t="str">
+            <v>Ecuador_Colombia</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="L125" t="str">
+            <v>Ecuador_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="L126" t="str">
+            <v>Ecuador_El Salvador</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="L127" t="str">
+            <v>Ecuador_Guatemala</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="L128" t="str">
+            <v>Ecuador_Honduras</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="L129" t="str">
+            <v>Ecuador_Mexico</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="L130" t="str">
+            <v>Ecuador_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="L131" t="str">
+            <v>Ecuador_Panama</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="L132" t="str">
+            <v>Ecuador_Paraguay</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="L133" t="str">
+            <v>Ecuador_Peru</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="L134" t="str">
+            <v>Ecuador_United States</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="L135" t="str">
+            <v>Ecuador_Uruguay</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="L136" t="str">
+            <v>Ecuador_Venezuela</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="L137" t="str">
+            <v>El Salvador_Argentina</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="L138" t="str">
+            <v>El Salvador_Bolivia</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="L139" t="str">
+            <v>El Salvador_Brazil</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="L140" t="str">
+            <v>El Salvador_Canada</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="L141" t="str">
+            <v>El Salvador_Chile</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="L142" t="str">
+            <v>El Salvador_Colombia</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="L143" t="str">
+            <v>El Salvador_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="L144" t="str">
+            <v>El Salvador_Ecuador</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="L145" t="str">
+            <v>El Salvador_Guatemala</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="L146" t="str">
+            <v>El Salvador_Honduras</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="L147" t="str">
+            <v>El Salvador_Mexico</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="L148" t="str">
+            <v>El Salvador_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="L149" t="str">
+            <v>El Salvador_Panama</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="L150" t="str">
+            <v>El Salvador_Paraguay</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="L151" t="str">
+            <v>El Salvador_Peru</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="L152" t="str">
+            <v>El Salvador_United States</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="L153" t="str">
+            <v>El Salvador_Uruguay</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="L154" t="str">
+            <v>El Salvador_Venezuela</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="L155" t="str">
+            <v>Guatemala_Argentina</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="L156" t="str">
+            <v>Guatemala_Bolivia</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="L157" t="str">
+            <v>Guatemala_Brazil</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="L158" t="str">
+            <v>Guatemala_Canada</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="L159" t="str">
+            <v>Guatemala_Chile</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="L160" t="str">
+            <v>Guatemala_Colombia</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="L161" t="str">
+            <v>Guatemala_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="L162" t="str">
+            <v>Guatemala_Ecuador</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="L163" t="str">
+            <v>Guatemala_El Salvador</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="L164" t="str">
+            <v>Guatemala_Honduras</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="L165" t="str">
+            <v>Guatemala_Mexico</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="L166" t="str">
+            <v>Guatemala_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="L167" t="str">
+            <v>Guatemala_Panama</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="L168" t="str">
+            <v>Guatemala_Paraguay</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="L169" t="str">
+            <v>Guatemala_Peru</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="L170" t="str">
+            <v>Guatemala_United States</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="L171" t="str">
+            <v>Guatemala_Uruguay</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="L172" t="str">
+            <v>Guatemala_Venezuela</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="L173" t="str">
+            <v>Honduras_Argentina</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="L174" t="str">
+            <v>Honduras_Bolivia</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="L175" t="str">
+            <v>Honduras_Brazil</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="L176" t="str">
+            <v>Honduras_Canada</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="L177" t="str">
+            <v>Honduras_Chile</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="L178" t="str">
+            <v>Honduras_Colombia</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="L179" t="str">
+            <v>Honduras_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="L180" t="str">
+            <v>Honduras_Ecuador</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="L181" t="str">
+            <v>Honduras_El Salvador</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="L182" t="str">
+            <v>Honduras_Guatemala</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="L183" t="str">
+            <v>Honduras_Mexico</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="L184" t="str">
+            <v>Honduras_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="L185" t="str">
+            <v>Honduras_Panama</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="L186" t="str">
+            <v>Honduras_Paraguay</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="L187" t="str">
+            <v>Honduras_Peru</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="L188" t="str">
+            <v>Honduras_United States</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="L189" t="str">
+            <v>Honduras_Uruguay</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="L190" t="str">
+            <v>Honduras_Venezuela</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="L191" t="str">
+            <v>Mexico_Argentina</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="L192" t="str">
+            <v>Mexico_Bolivia</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="L193" t="str">
+            <v>Mexico_Brazil</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="L194" t="str">
+            <v>Mexico_Canada</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="L195" t="str">
+            <v>Mexico_Chile</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="L196" t="str">
+            <v>Mexico_Colombia</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="L197" t="str">
+            <v>Mexico_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="L198" t="str">
+            <v>Mexico_Ecuador</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="L199" t="str">
+            <v>Mexico_El Salvador</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="L200" t="str">
+            <v>Mexico_Guatemala</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="L201" t="str">
+            <v>Mexico_Honduras</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="L202" t="str">
+            <v>Mexico_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="L203" t="str">
+            <v>Mexico_Panama</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="L204" t="str">
+            <v>Mexico_Paraguay</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="L205" t="str">
+            <v>Mexico_Peru</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="L206" t="str">
+            <v>Mexico_United States</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="L207" t="str">
+            <v>Mexico_Uruguay</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="L208" t="str">
+            <v>Mexico_Venezuela</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="L209" t="str">
+            <v>Nicaragua_Argentina</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="L210" t="str">
+            <v>Nicaragua_Bolivia</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="L211" t="str">
+            <v>Nicaragua_Brazil</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="L212" t="str">
+            <v>Nicaragua_Canada</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="L213" t="str">
+            <v>Nicaragua_Chile</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="L214" t="str">
+            <v>Nicaragua_Colombia</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="L215" t="str">
+            <v>Nicaragua_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="L216" t="str">
+            <v>Nicaragua_Ecuador</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="L217" t="str">
+            <v>Nicaragua_El Salvador</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="L218" t="str">
+            <v>Nicaragua_Guatemala</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="L219" t="str">
+            <v>Nicaragua_Honduras</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="L220" t="str">
+            <v>Nicaragua_Mexico</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="L221" t="str">
+            <v>Nicaragua_Panama</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="L222" t="str">
+            <v>Nicaragua_Peru</v>
+          </cell>
+        </row>
+        <row r="223">
+          <cell r="L223" t="str">
+            <v>Nicaragua_United States</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="L224" t="str">
+            <v>Nicaragua_Uruguay</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="L225" t="str">
+            <v>Nicaragua_Venezuela</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="L226" t="str">
+            <v>Panama_Argentina</v>
+          </cell>
+        </row>
+        <row r="227">
+          <cell r="L227" t="str">
+            <v>Panama_Bolivia</v>
+          </cell>
+        </row>
+        <row r="228">
+          <cell r="L228" t="str">
+            <v>Panama_Brazil</v>
+          </cell>
+        </row>
+        <row r="229">
+          <cell r="L229" t="str">
+            <v>Panama_Canada</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="L230" t="str">
+            <v>Panama_Chile</v>
+          </cell>
+        </row>
+        <row r="231">
+          <cell r="L231" t="str">
+            <v>Panama_Colombia</v>
+          </cell>
+        </row>
+        <row r="232">
+          <cell r="L232" t="str">
+            <v>Panama_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="L233" t="str">
+            <v>Panama_Ecuador</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="L234" t="str">
+            <v>Panama_El Salvador</v>
+          </cell>
+        </row>
+        <row r="235">
+          <cell r="L235" t="str">
+            <v>Panama_Guatemala</v>
+          </cell>
+        </row>
+        <row r="236">
+          <cell r="L236" t="str">
+            <v>Panama_Honduras</v>
+          </cell>
+        </row>
+        <row r="237">
+          <cell r="L237" t="str">
+            <v>Panama_Mexico</v>
+          </cell>
+        </row>
+        <row r="238">
+          <cell r="L238" t="str">
+            <v>Panama_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="239">
+          <cell r="L239" t="str">
+            <v>Panama_Paraguay</v>
+          </cell>
+        </row>
+        <row r="240">
+          <cell r="L240" t="str">
+            <v>Panama_Peru</v>
+          </cell>
+        </row>
+        <row r="241">
+          <cell r="L241" t="str">
+            <v>Panama_United States</v>
+          </cell>
+        </row>
+        <row r="242">
+          <cell r="L242" t="str">
+            <v>Panama_Uruguay</v>
+          </cell>
+        </row>
+        <row r="243">
+          <cell r="L243" t="str">
+            <v>Panama_Venezuela</v>
+          </cell>
+        </row>
+        <row r="244">
+          <cell r="L244" t="str">
+            <v>Paraguay_Argentina</v>
+          </cell>
+        </row>
+        <row r="245">
+          <cell r="L245" t="str">
+            <v>Paraguay_Bolivia</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="L246" t="str">
+            <v>Paraguay_Brazil</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="L247" t="str">
+            <v>Paraguay_Canada</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="L248" t="str">
+            <v>Paraguay_Chile</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="L249" t="str">
+            <v>Paraguay_Mexico</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="L250" t="str">
+            <v>Paraguay_United States</v>
+          </cell>
+        </row>
+        <row r="251">
+          <cell r="L251" t="str">
+            <v>Paraguay_Uruguay</v>
+          </cell>
+        </row>
+        <row r="252">
+          <cell r="L252" t="str">
+            <v>Peru_Argentina</v>
+          </cell>
+        </row>
+        <row r="253">
+          <cell r="L253" t="str">
+            <v>Peru_Bolivia</v>
+          </cell>
+        </row>
+        <row r="254">
+          <cell r="L254" t="str">
+            <v>Peru_Brazil</v>
+          </cell>
+        </row>
+        <row r="255">
+          <cell r="L255" t="str">
+            <v>Peru_Canada</v>
+          </cell>
+        </row>
+        <row r="256">
+          <cell r="L256" t="str">
+            <v>Peru_Chile</v>
+          </cell>
+        </row>
+        <row r="257">
+          <cell r="L257" t="str">
+            <v>Peru_Colombia</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="L258" t="str">
+            <v>Peru_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="L259" t="str">
+            <v>Peru_Ecuador</v>
+          </cell>
+        </row>
+        <row r="260">
+          <cell r="L260" t="str">
+            <v>Peru_El Salvador</v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="L261" t="str">
+            <v>Peru_Guatemala</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="L262" t="str">
+            <v>Peru_Honduras</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="L263" t="str">
+            <v>Peru_Mexico</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="L264" t="str">
+            <v>Peru_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="L265" t="str">
+            <v>Peru_Panama</v>
+          </cell>
+        </row>
+        <row r="266">
+          <cell r="L266" t="str">
+            <v>Peru_Paraguay</v>
+          </cell>
+        </row>
+        <row r="267">
+          <cell r="L267" t="str">
+            <v>Peru_United States</v>
+          </cell>
+        </row>
+        <row r="268">
+          <cell r="L268" t="str">
+            <v>Peru_Uruguay</v>
+          </cell>
+        </row>
+        <row r="269">
+          <cell r="L269" t="str">
+            <v>Peru_Venezuela</v>
+          </cell>
+        </row>
+        <row r="270">
+          <cell r="L270" t="str">
+            <v>United States_Argentina</v>
+          </cell>
+        </row>
+        <row r="271">
+          <cell r="L271" t="str">
+            <v>United States_Bolivia</v>
+          </cell>
+        </row>
+        <row r="272">
+          <cell r="L272" t="str">
+            <v>United States_Brazil</v>
+          </cell>
+        </row>
+        <row r="273">
+          <cell r="L273" t="str">
+            <v>United States_Canada</v>
+          </cell>
+        </row>
+        <row r="274">
+          <cell r="L274" t="str">
+            <v>United States_Chile</v>
+          </cell>
+        </row>
+        <row r="275">
+          <cell r="L275" t="str">
+            <v>United States_Colombia</v>
+          </cell>
+        </row>
+        <row r="276">
+          <cell r="L276" t="str">
+            <v>United States_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="277">
+          <cell r="L277" t="str">
+            <v>United States_Ecuador</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="L278" t="str">
+            <v>United States_El Salvador</v>
+          </cell>
+        </row>
+        <row r="279">
+          <cell r="L279" t="str">
+            <v>United States_Guatemala</v>
+          </cell>
+        </row>
+        <row r="280">
+          <cell r="L280" t="str">
+            <v>United States_Honduras</v>
+          </cell>
+        </row>
+        <row r="281">
+          <cell r="L281" t="str">
+            <v>United States_Mexico</v>
+          </cell>
+        </row>
+        <row r="282">
+          <cell r="L282" t="str">
+            <v>United States_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="283">
+          <cell r="L283" t="str">
+            <v>United States_Panama</v>
+          </cell>
+        </row>
+        <row r="284">
+          <cell r="L284" t="str">
+            <v>United States_Paraguay</v>
+          </cell>
+        </row>
+        <row r="285">
+          <cell r="L285" t="str">
+            <v>United States_Peru</v>
+          </cell>
+        </row>
+        <row r="286">
+          <cell r="L286" t="str">
+            <v>United States_Uruguay</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="L287" t="str">
+            <v>United States_Venezuela</v>
+          </cell>
+        </row>
+        <row r="288">
+          <cell r="L288" t="str">
+            <v>Uruguay_Argentina</v>
+          </cell>
+        </row>
+        <row r="289">
+          <cell r="L289" t="str">
+            <v>Uruguay_Brazil</v>
+          </cell>
+        </row>
+        <row r="290">
+          <cell r="L290" t="str">
+            <v>Uruguay_Canada</v>
+          </cell>
+        </row>
+        <row r="291">
+          <cell r="L291" t="str">
+            <v>Uruguay_Chile</v>
+          </cell>
+        </row>
+        <row r="292">
+          <cell r="L292" t="str">
+            <v>Uruguay_Mexico</v>
+          </cell>
+        </row>
+        <row r="293">
+          <cell r="L293" t="str">
+            <v>Uruguay_Paraguay</v>
+          </cell>
+        </row>
+        <row r="294">
+          <cell r="L294" t="str">
+            <v>Uruguay_Peru</v>
+          </cell>
+        </row>
+        <row r="295">
+          <cell r="L295" t="str">
+            <v>Uruguay_United States</v>
+          </cell>
+        </row>
+        <row r="296">
+          <cell r="L296" t="str">
+            <v>Uruguay_Venezuela</v>
+          </cell>
+        </row>
+        <row r="297">
+          <cell r="L297" t="str">
+            <v>Venezuela_Argentina</v>
+          </cell>
+        </row>
+        <row r="298">
+          <cell r="L298" t="str">
+            <v>Venezuela_Bolivia</v>
+          </cell>
+        </row>
+        <row r="299">
+          <cell r="L299" t="str">
+            <v>Venezuela_Brazil</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="L300" t="str">
+            <v>Venezuela_Canada</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="L301" t="str">
+            <v>Venezuela_Chile</v>
+          </cell>
+        </row>
+        <row r="302">
+          <cell r="L302" t="str">
+            <v>Venezuela_Colombia</v>
+          </cell>
+        </row>
+        <row r="303">
+          <cell r="L303" t="str">
+            <v>Venezuela_Costa Rica</v>
+          </cell>
+        </row>
+        <row r="304">
+          <cell r="L304" t="str">
+            <v>Venezuela_Ecuador</v>
+          </cell>
+        </row>
+        <row r="305">
+          <cell r="L305" t="str">
+            <v>Venezuela_El Salvador</v>
+          </cell>
+        </row>
+        <row r="306">
+          <cell r="L306" t="str">
+            <v>Venezuela_Guatemala</v>
+          </cell>
+        </row>
+        <row r="307">
+          <cell r="L307" t="str">
+            <v>Venezuela_Honduras</v>
+          </cell>
+        </row>
+        <row r="308">
+          <cell r="L308" t="str">
+            <v>Venezuela_Mexico</v>
+          </cell>
+        </row>
+        <row r="309">
+          <cell r="L309" t="str">
+            <v>Venezuela_Nicaragua</v>
+          </cell>
+        </row>
+        <row r="310">
+          <cell r="L310" t="str">
+            <v>Venezuela_Panama</v>
+          </cell>
+        </row>
+        <row r="311">
+          <cell r="L311" t="str">
+            <v>Venezuela_Paraguay</v>
+          </cell>
+        </row>
+        <row r="312">
+          <cell r="L312" t="str">
+            <v>Venezuela_Peru</v>
+          </cell>
+        </row>
+        <row r="313">
+          <cell r="L313" t="str">
+            <v>Venezuela_United States</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="L314" t="str">
+            <v>Venezuela_Uruguay</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,6 +2119,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D29F23F2-F4BA-4513-96CB-92CF9D613F15}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
@@ -626,1090 +2198,1537 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>28095</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>27597</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>13698</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>45770</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2582</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1120</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2239</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>166</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>350</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>142</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>6625</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>188</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>796</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>64404</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>8282</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>128397</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>21691</v>
       </c>
-      <c r="T2" s="8">
-        <v>9483</v>
+      <c r="T2" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A2,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>8724</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>226137</v>
       </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>20437</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2397</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>10568</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>671</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>282</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>634</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>44</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>86</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>110</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2007</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>46</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>189</v>
       </c>
-      <c r="P3" s="5">
+      <c r="P3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1140</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4174</v>
       </c>
-      <c r="R3" s="6">
+      <c r="R3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>54630</v>
       </c>
-      <c r="S3" s="6">
-        <v>11507</v>
-      </c>
-      <c r="T3" s="8">
-        <v>2224</v>
+      <c r="S3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A3,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>1838</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>32925</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>14801</v>
       </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>13327</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>6886</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1889</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>415</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1101</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>198</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>151</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>176</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3391</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>107</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>802</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>83208</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3545</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>217822</v>
       </c>
-      <c r="S4" s="6">
-        <v>355</v>
-      </c>
-      <c r="T4" s="8">
-        <v>4323</v>
+      <c r="S4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>11507</v>
+      </c>
+      <c r="T4" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A4,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>4828</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1110</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1672</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1256</v>
       </c>
-      <c r="E5" s="5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="7">
+      <c r="E5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>780</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1074</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>971</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>249</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>251</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>259</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>7245</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>180</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>438</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2575</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>893</v>
       </c>
-      <c r="R5" s="6">
+      <c r="R5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>841612</v>
       </c>
-      <c r="S5" s="6">
-        <v>1455</v>
-      </c>
-      <c r="T5" s="8">
-        <v>981</v>
+      <c r="S5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>355</v>
+      </c>
+      <c r="T5" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A5,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>964</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>205945</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4388</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>17172</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>24970</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="7">
+      <c r="F6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1761</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1327</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4702</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>207</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>191</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>230</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5685</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>111</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1060</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2382</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5239</v>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>82855</v>
       </c>
-      <c r="S6" s="6">
-        <v>602</v>
-      </c>
-      <c r="T6" s="8">
-        <v>22198</v>
+      <c r="S6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>1455</v>
+      </c>
+      <c r="T6" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A6,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>15733</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3622</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1342</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4169</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>17942</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3913</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="5">
+      <c r="G7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5995</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>71556</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>363</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>730</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>644</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>6639</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>309</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>21473</v>
       </c>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="6">
+      <c r="P7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4331</v>
       </c>
-      <c r="R7" s="6">
+      <c r="R7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>522819</v>
       </c>
-      <c r="S7" s="6">
-        <v>1160</v>
-      </c>
-      <c r="T7" s="8">
-        <v>555578</v>
+      <c r="S7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A7,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>617257</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>257</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>141</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>239</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2476</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="7">
+      <c r="F8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>822</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5">
+      <c r="H8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>389</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>818</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>734</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>639</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3166</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>6948</v>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4654</v>
       </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="6">
+      <c r="P8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>246</v>
       </c>
-      <c r="R8" s="6">
+      <c r="R8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>73694</v>
       </c>
-      <c r="S8" s="6">
-        <v>104</v>
-      </c>
-      <c r="T8" s="8">
-        <v>1661</v>
+      <c r="S8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A8,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>1178</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2004</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>738</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1191</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>11261</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>8857</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>11964</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>971</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="6">
+      <c r="I9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>97</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>105</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>342</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1778</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>86</v>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1896</v>
       </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="6">
+      <c r="P9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2911</v>
       </c>
-      <c r="R9" s="6">
+      <c r="R9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>306208</v>
       </c>
-      <c r="S9" s="6">
-        <v>705</v>
-      </c>
-      <c r="T9" s="8">
-        <v>24600</v>
+      <c r="S9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A9,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>28999</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>156</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>107</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>481</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>38826</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="7">
+      <c r="F10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>315</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>8857</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>217</v>
       </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="5">
+      <c r="J10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>12037</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>6574</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5786</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2102</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2032</v>
       </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="6">
+      <c r="P10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>79</v>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>838090</v>
       </c>
-      <c r="S10" s="6">
-        <v>659</v>
-      </c>
-      <c r="T10" s="8">
-        <v>1017</v>
+      <c r="S10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A10,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>908</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>201</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>141</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>158</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>13960</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="7">
+      <c r="F11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>346</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2029</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>179</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>6212</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6">
+      <c r="K11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3421</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>29156</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1199</v>
       </c>
-      <c r="O11" s="5">
+      <c r="O11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>600</v>
       </c>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="6">
+      <c r="P11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>119</v>
       </c>
-      <c r="R11" s="6">
+      <c r="R11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>492870</v>
       </c>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8">
-        <v>579</v>
+      <c r="S11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T11" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A11,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>139</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>197</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>136</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4462</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="7">
+      <c r="F12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>286</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2994</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>195</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>9525</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5295</v>
       </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="5">
+      <c r="L12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4203</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>10017</v>
       </c>
-      <c r="O12" s="5">
+      <c r="O12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>838</v>
       </c>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="6">
+      <c r="P12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>121</v>
       </c>
-      <c r="R12" s="6">
+      <c r="R12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>290034</v>
       </c>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8">
-        <v>437</v>
+      <c r="S12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A12,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3040</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>9323</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1261</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>42332</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1700</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2236</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2365</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>937</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1438</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>11070</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1164</v>
       </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6">
+      <c r="M13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>725</v>
       </c>
-      <c r="O13" s="5">
+      <c r="O13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2341</v>
       </c>
-      <c r="P13" s="5">
+      <c r="P13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1813</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="Q13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1088</v>
       </c>
-      <c r="R13" s="6">
+      <c r="R13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>9410529</v>
       </c>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8">
-        <v>2886</v>
+      <c r="S13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>602</v>
+      </c>
+      <c r="T13" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A13,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>3115</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>190</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>85</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>501</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>9444</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="5">
+      <c r="F14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>230085</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>163</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4545</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5404</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5768</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3696</v>
       </c>
-      <c r="N14" s="6"/>
-      <c r="O14" s="5">
+      <c r="N14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4923</v>
       </c>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="6">
+      <c r="P14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>117</v>
       </c>
-      <c r="R14" s="6">
+      <c r="R14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>225929</v>
       </c>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8">
-        <v>2526</v>
+      <c r="S14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A14,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>1934</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>338</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>97</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>559</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2495</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="7">
+      <c r="F15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1858</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>10438</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>400</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>354</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>190</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>296</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2396</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>347</v>
       </c>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="6">
+      <c r="O15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>252</v>
       </c>
-      <c r="R15" s="6">
+      <c r="R15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>107847</v>
       </c>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8">
-        <v>1470</v>
+      <c r="S15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A15,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>976</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>315086</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3236</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>28891</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4972</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1198</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="5">
+      <c r="G16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>63</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>101</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>15</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>38</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>26</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>329</v>
       </c>
-      <c r="N16" s="6"/>
-      <c r="O16" s="5">
+      <c r="N16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>35</v>
       </c>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="6">
+      <c r="P16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>398</v>
       </c>
-      <c r="R16" s="6">
+      <c r="R16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>12284</v>
       </c>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8">
-        <v>359</v>
+      <c r="S16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>1160</v>
+      </c>
+      <c r="T16" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A16,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>85411</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>9386</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>10840</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>17932</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>35460</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3788</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2887</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5682</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>172</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>288</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>285</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5479</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>185</v>
       </c>
-      <c r="O17" s="5">
+      <c r="O17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2697</v>
       </c>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6">
+      <c r="P17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>285249</v>
       </c>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8">
-        <v>29635</v>
+      <c r="S17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>104</v>
+      </c>
+      <c r="T17" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A17,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>36348</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>9364</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3656</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>13981</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>255952</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>7884</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>15068</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>9667</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>11112</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4603</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5456</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5061</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>358399</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3006</v>
       </c>
-      <c r="O18" s="5">
+      <c r="O18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>5212</v>
       </c>
-      <c r="P18" s="5">
+      <c r="P18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1781</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="Q18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>7188</v>
       </c>
-      <c r="R18" s="6"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8">
-        <v>11639</v>
+      <c r="R18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>705</v>
+      </c>
+      <c r="T18" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A18,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>10159</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>113827</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>453</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>24799</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>6240</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2238</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>364</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>239</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>398</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>67</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>89</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>50</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1966</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>21</v>
       </c>
-      <c r="O19" s="5">
+      <c r="O19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>264</v>
       </c>
-      <c r="P19" s="5">
+      <c r="P19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3303</v>
       </c>
-      <c r="Q19" s="6">
+      <c r="Q19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>447</v>
       </c>
-      <c r="R19" s="6">
+      <c r="R19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>25673</v>
       </c>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8">
-        <v>6076</v>
+      <c r="S19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A19,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>4692</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(B$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2600</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(C$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>543</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(D$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2167</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(E$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>7958</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(F$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>4044</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(G$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>37200</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(H$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>1054</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(I$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3691</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(J$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>179</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(K$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>175</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(L$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>73</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(M$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>3024</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(N$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>125</v>
       </c>
-      <c r="O20" s="5">
+      <c r="O20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(O$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>989</v>
       </c>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="6">
+      <c r="P20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(P$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(Q$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>2362</v>
       </c>
-      <c r="R20" s="6">
+      <c r="R20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(R$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>109748</v>
       </c>
-      <c r="S20" s="8"/>
+      <c r="S20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(S$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
+        <v>659</v>
+      </c>
       <c r="T20" s="4">
+        <f ca="1">_xlfn.IFNA(OFFSET([1]Sheet1!$G$1,MATCH(T$1&amp;"_"&amp;$A20,[1]Sheet1!$L:$L,0)-1,0),0)</f>
         <v>0</v>
       </c>
     </row>
